--- a/demos/public_good_experiment/public_good_experiment_prompt_template.xlsx
+++ b/demos/public_good_experiment/public_good_experiment_prompt_template.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raymondlow/Documents/talking-to-machines/talking-to-machines/demos/public_good_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9672724-2862-8848-9024-BD3AD8B23135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231100AC-0422-4440-A56D-0B65BF63409F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5800" yWindow="-20740" windowWidth="30760" windowHeight="20140" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="2600" windowWidth="34560" windowHeight="19720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="experimental_setting" sheetId="1" r:id="rId1"/>
-    <sheet name="treatments" sheetId="2" r:id="rId2"/>
-    <sheet name="roles" sheetId="3" r:id="rId3"/>
-    <sheet name="interview_prompts" sheetId="4" r:id="rId4"/>
-    <sheet name="demographic_profiles" sheetId="5" r:id="rId5"/>
-    <sheet name="constants" sheetId="6" r:id="rId6"/>
+    <sheet name="settings" sheetId="1" r:id="rId1"/>
+    <sheet name="treatment" sheetId="2" r:id="rId2"/>
+    <sheet name="role" sheetId="3" r:id="rId3"/>
+    <sheet name="prompt" sheetId="4" r:id="rId4"/>
+    <sheet name="profile" sheetId="5" r:id="rId5"/>
+    <sheet name="constant" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">demographic_profiles!$A$1:$Y$5312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">profile!$A$1:$Y$5312</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,24 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
-  <si>
-    <t>experimental_setting</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="121">
   <si>
     <t>value</t>
   </si>
   <si>
-    <t>experiment_id</t>
-  </si>
-  <si>
     <t>model_info</t>
-  </si>
-  <si>
-    <t>num_sessions</t>
-  </si>
-  <si>
-    <t>max_conversation_length</t>
   </si>
   <si>
     <t>treatment_assignment_strategy</t>
@@ -60,9 +48,6 @@
   </si>
   <si>
     <t>treatment</t>
-  </si>
-  <si>
-    <t>session_assignment_strategy</t>
   </si>
   <si>
     <t>role_assignment_strategy</t>
@@ -77,19 +62,7 @@
     <t>role_label</t>
   </si>
   <si>
-    <t>role_description</t>
-  </si>
-  <si>
-    <t>Participant 1</t>
-  </si>
-  <si>
-    <t>task_id</t>
-  </si>
-  <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>task_order</t>
   </si>
   <si>
     <t>is_adapted</t>
@@ -99,12 +72,6 @@
   </si>
   <si>
     <t>llm_text</t>
-  </si>
-  <si>
-    <t>var_name</t>
-  </si>
-  <si>
-    <t>var_type</t>
   </si>
   <si>
     <t>response_options</t>
@@ -131,13 +98,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>random_seed</t>
-  </si>
-  <si>
-    <t>session_column</t>
   </si>
   <si>
     <t>role_column</t>
@@ -153,93 +114,6 @@
   </si>
   <si>
     <t>private_question</t>
-  </si>
-  <si>
-    <t>include_backstories</t>
-  </si>
-  <si>
-    <t>gpt-4.1</t>
-  </si>
-  <si>
-    <t>session</t>
-  </si>
-  <si>
-    <t>Treatment 1</t>
-  </si>
-  <si>
-    <t>Treatment description 1</t>
-  </si>
-  <si>
-    <t>Treatment 2</t>
-  </si>
-  <si>
-    <t>Treatment description 2</t>
-  </si>
-  <si>
-    <t>Summarizer</t>
-  </si>
-  <si>
-    <t>Assume the role of a summariser in a public good experiment involving 4 {{participant_label}}s. Each {{participant_label}} will start with an initial endowment of 10 tokens. During each round of the experiment, each {{participant_label}} is asked to decide how many tokens to contribute to a public account and how many to keep in their private account. The tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in the {{participant_label}}s' private account will not be shared and remain private. 
-Example:
-A {{participant_label}} have 10 tokens. If that {{participant_label}} contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). The {{participant_label}} will keep the remaining 6 tokens in their private account. Contributions to the public account benefit everyone, including the {{participant_label}}. What they keep in their private account benefits only themselves. The total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you are responsible for calculating the following information for each {{participant_label}}:
-- The total tokens contributed to the public account by all {{participant_label}}s.
-- The {{participant_label}}'s earnings from the public account.
-- The {{participant_label}}'s private tokens kept from the round.
-- The {{participant_label}}'s total earnings so far.</t>
-  </si>
-  <si>
-    <t>Assume the role of a {{participant_label}} (Participant 1) in a public good experiment involving 3 other {{participant_label}}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{participant_label}}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.</t>
-  </si>
-  <si>
-    <t>Participant 2</t>
-  </si>
-  <si>
-    <t>Assume the role of a {{participant_label}} (Participant 2) in a public good experiment involving 3 other {{participant_label}}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{participant_label}}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.</t>
-  </si>
-  <si>
-    <t>Participant 3</t>
-  </si>
-  <si>
-    <t>Assume the role of a {{participant_label}} (Participant 3) in a public good experiment involving 3 other {{participant_label}}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{participant_label}}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.</t>
-  </si>
-  <si>
-    <t>Participant 4</t>
-  </si>
-  <si>
-    <t>Assume the role of a {{participant_label}} (Participant 4) in a public good experiment involving 3 other {{participant_label}}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{participant_label}}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.</t>
   </si>
   <si>
     <t>participant_label</t>
@@ -365,8 +239,93 @@
     <t>Are you a republican?</t>
   </si>
   <si>
+    <t>Please answer the following questions to ensure you understand the rules. If you contribute 5 tokens to the public account, how many total tokens will be in the public account before it is shared?</t>
+  </si>
+  <si>
+    <t>Please answer the following questions to ensure you understand the rules. How are tokens from the public account distributed to group members?</t>
+  </si>
+  <si>
+    <t>Please answer the following questions to ensure you understand the rules. If you keep all your tokens in your private account, what happens to the tokens in the public account?</t>
+  </si>
+  <si>
+    <t>How many tokens do you want to contribute to the public account? (Enter a number between 0 and 10)</t>
+  </si>
+  <si>
+    <t>comprehension_qn_1</t>
+  </si>
+  <si>
+    <t>comprehension_qn_2</t>
+  </si>
+  <si>
+    <t>comprehension_qn_3</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>[10, 15, 20, 25]</t>
+  </si>
+  <si>
+    <t>["Equally among all members", "Based on individual contributions", "Randomly assigned", "Not distributed at all"]</t>
+  </si>
+  <si>
+    <t>["You receive nothing from the public account", "The total tokens in the public account decrease", "Other group members’ earnings increase", "None of the above"]</t>
+  </si>
+  <si>
+    <t>hf_inference_endpoint</t>
+  </si>
+  <si>
+    <t>public_good_experiment</t>
+  </si>
+  <si>
+    <t>session_id</t>
+  </si>
+  <si>
+    <t>num_groups</t>
+  </si>
+  <si>
+    <t>num_subjects_per_group</t>
+  </si>
+  <si>
+    <t>group_assignment_strategy</t>
+  </si>
+  <si>
+    <t>group_column</t>
+  </si>
+  <si>
+    <t>build_profile_qna</t>
+  </si>
+  <si>
+    <t>build_profile_backstories</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>round_decision</t>
+  </si>
+  <si>
+    <t>{{ treatment.description }}</t>
+  </si>
+  <si>
+    <t>repeat_private_question</t>
+  </si>
+  <si>
+    <t>facilitator</t>
+  </si>
+  <si>
+    <t>{
+"description":"Description for Treatment 2."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Description for Treatment 1."
+}</t>
+  </si>
+  <si>
     <t xml:space="preserve">General Overview
-Welcome to the public good experiment. You will be part of a group of 4 {{participant_label}}, and you will interact with the same group throughout the experiment. The experiment consists of 5 rounds, and your decisions will affect both your earnings and the earnings of others in your group. All decisions are anonymous, and you will not know the identity of other participants.
+Welcome to the public good experiment. You will be part of a group of 4 participants, and you will interact with the same group throughout the experiment. The experiment consists of 5 rounds, and your decisions will affect both your earnings and the earnings of others in your group. All decisions are anonymous, and you will not know the identity of other participants.
 1. Instructions
 Your group will start with an initial endowment of 10 tokens.
 You must decide how many tokens to contribute to a public account and how many to keep in your private account.
@@ -389,20 +348,93 @@
 </t>
   </si>
   <si>
-    <t>Please answer the following questions to ensure you understand the rules. If you contribute 5 tokens to the public account, how many total tokens will be in the public account before it is shared?</t>
+    <t>settings_label</t>
   </si>
   <si>
-    <t>Please answer the following questions to ensure you understand the rules. How are tokens from the public account distributed to group members?</t>
+    <t>constant_label</t>
   </si>
   <si>
-    <t>Please answer the following questions to ensure you understand the rules. If you keep all your tokens in your private account, what happens to the tokens in the public account?</t>
+    <t>Please answer the following questions to ensure you understand the rules. If you contribute 5 tokens to the public account, how many total tokens will be in the public account before it is shared? {{ response_options }}</t>
   </si>
   <si>
-    <t>How many tokens do you want to contribute to the public account? (Enter a number between 0 and 10)</t>
+    <t>Please answer the following questions to ensure you understand the rules. How are tokens from the public account distributed to group members? {{ response_options }}</t>
+  </si>
+  <si>
+    <t>Please answer the following questions to ensure you understand the rules. If you keep all your tokens in your private account, what happens to the tokens in the public account? {{ response_options }}</t>
+  </si>
+  <si>
+    <t>round_id</t>
+  </si>
+  <si>
+    <t>round_order</t>
+  </si>
+  <si>
+    <t>response_name</t>
+  </si>
+  <si>
+    <t>response_type</t>
+  </si>
+  <si>
+    <t>gpt-5-mini</t>
+  </si>
+  <si>
+    <t>max_num_rounds</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 1) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
+Example: 
+You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
+At the end of each round, you will see:
+- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
+- Your earnings from the public account.
+- Your private tokens kept from the round.
+- Your total earnings so far.
+Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 2) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
+Example: 
+You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
+At the end of each round, you will see:
+- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
+- Your earnings from the public account.
+- Your private tokens kept from the round.
+- Your total earnings so far.
+Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 3) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
+Example: 
+You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
+At the end of each round, you will see:
+- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
+- Your earnings from the public account.
+- Your private tokens kept from the round.
+- Your total earnings so far.
+Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 4) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
+Example: 
+You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
+At the end of each round, you will see:
+- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
+- Your earnings from the public account.
+- Your private tokens kept from the round.
+- Your total earnings so far.
+Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
+}</t>
   </si>
   <si>
     <t xml:space="preserve">General Overview
-Welcome to the public good experiment. You will be part of a group of 4 {{participant_label}}s, and you will interact with the same group throughout the experiment. The experiment consists of 5 rounds, and your decisions will affect both your earnings and the earnings of others in your group. All decisions are anonymous, and you will not know the identity of other {{participant_label}}s.
+Welcome to the public good experiment. You will be part of a group of 4 {{ constant.participant_label }}s, and you will interact with the same group throughout the experiment. The experiment consists of 5 rounds, and your decisions will affect both your earnings and the earnings of others in your group. All decisions are anonymous, and you will not know the identity of other {{ constant.participant_label }}s.
 1. Instructions
 Your group will start with an initial endowment of 10 tokens.
 You must decide how many tokens to contribute to a public account and how many to keep in your private account.
@@ -425,82 +457,53 @@
 </t>
   </si>
   <si>
-    <t>Please answer the following questions to ensure you understand the rules. If you contribute 5 tokens to the public account, how many total tokens will be in the public account before it is shared? {response_options}</t>
+    <t>Participant 1</t>
   </si>
   <si>
-    <t>Please answer the following questions to ensure you understand the rules. How are tokens from the public account distributed to group members? {response_options}</t>
+    <t>Participant 2</t>
   </si>
   <si>
-    <t>Please answer the following questions to ensure you understand the rules. If you keep all your tokens in your private account, what happens to the tokens in the public account? {response_options}</t>
+    <t>Participant 3</t>
   </si>
   <si>
-    <t>{"Participant 1": "How many tokens do you want to contribute to the public account? {response_options}", "Participant 2": "How many tokens do you want to contribute to the public account? {response_options}", "Participant 3": "How many tokens do you want to contribute to the public account? {response_options}", "Participant 4": "How many tokens do you want to contribute to the public account? {response_options}", "Summarizer": "Calculate the following information for each participant in the following format:\n- The total tokens contributed to the public account by all participants:\n- The participant's earnings from the public account:\n- The participant's private tokens kept from the round:\n- The participant's total earnings so far:"}</t>
-  </si>
-  <si>
-    <t>{"Participant 4": "How many tokens do you want to contribute to the public account? {response_options}", "Participant 3": "How many tokens do you want to contribute to the public account? {response_options}", "Participant 2": "How many tokens do you want to contribute to the public account? {response_options}", "Participant 1": "How many tokens do you want to contribute to the public account? {response_options}", "Summarizer": "Calculate the following information for each participant in the following format:\n- The total tokens contributed to the public account by all participants:\n- The participant's earnings from the public account:\n- The participant's private tokens kept from the round:\n- The participant's total earnings so far:"}</t>
-  </si>
-  <si>
-    <t>comprehension_qn_1</t>
-  </si>
-  <si>
-    <t>comprehension_qn_2</t>
-  </si>
-  <si>
-    <t>comprehension_qn_3</t>
-  </si>
-  <si>
-    <t>round_decision_1</t>
-  </si>
-  <si>
-    <t>round_decision_2</t>
-  </si>
-  <si>
-    <t>round_decision_3</t>
-  </si>
-  <si>
-    <t>round_decision_4</t>
-  </si>
-  <si>
-    <t>round_decision_5</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>[10, 15, 20, 25]</t>
-  </si>
-  <si>
-    <t>["Equally among all members", "Based on individual contributions", "Randomly assigned", "Not distributed at all"]</t>
-  </si>
-  <si>
-    <t>["You receive nothing from the public account", "The total tokens in the public account decrease", "Other group members’ earnings increase", "None of the above"]</t>
-  </si>
-  <si>
-    <t>(0,10)</t>
-  </si>
-  <si>
-    <t>Enter a number between 0 and 10</t>
-  </si>
-  <si>
-    <t>[0,1,2,3,4,5,6,7,8,9,10]</t>
+    <t>Participant 4</t>
   </si>
   <si>
     <t>{"Participant 1": "Enter a number between 0 and 10", "Participant 2": "Enter a number between 0 and 10", "Participant 3": (0,10), "Participant 4": [0,1,2,3,4,5,6,7,8,9,10]}</t>
   </si>
   <si>
-    <t>hf_inference_endpoint</t>
+    <t>{
+"Participant 1": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"Participant 2": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"Participant 3": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"Participant 4": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"facilitator": {{ role.calculate_payoff }},
+"facilitator": {{ role.end_round }},
+}</t>
   </si>
   <si>
-    <t>Assume the role of a facilitator in a public good experiment.</t>
+    <t>Treatment 1</t>
   </si>
   <si>
-    <t>Facilitator</t>
+    <t>Treatment 2</t>
   </si>
   <si>
-    <t>num_subjects_per_session</t>
-  </si>
-  <si>
-    <t>public_good_experiment</t>
+    <t>{
+"description":"Assume the role of a facilitator in a public good experiment involving 4 {{ constant.participant_label }}s. Each {{ constant.participant_label }} will start with an initial endowment of 10 tokens. During each round of the experiment, each {{ constant.participant_label }} is asked to decide how many tokens to contribute to a public account and how many to keep in their private account. The tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in the {{ constant.participant_label }}s' private account will not be shared and remain private. 
+Example:
+A {{ constant.participant_label }} have 10 tokens. If that {{ constant.participant_label }} contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). The {{ constant.participant_label }} will keep the remaining 6 tokens in their private account. Contributions to the public account benefit everyone, including the {{ constant.participant_label }}. What they keep in their private account benefits only themselves. The total earnings for each round equal to private tokens kept + public tokens earned.
+At the end of each round, you are responsible for calculating the following information for each {{ constant.participant_label }}:
+- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
+- The {{ constant.participant_label }}'s earnings from the public account.
+- The {{ constant.participant_label }}'s private tokens kept from the round.
+- The {{ constant.participant_label }}'s total earnings so far.", 
+"calculate_payoff":"Calculate the following information for each {{ constant.participant_label }}:
+- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
+- The {{ constant.participant_label }}'s earnings from the public account.
+- The {{ constant.participant_label }}'s private tokens kept from the round.
+- The {{ constant.participant_label }}'s total earnings so far.",
+"end_round":"Evaluate the number of times that the group has repeated this round and return the following command if the group has completed this round at least five times: 'end_round' "
+}</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1002"/>
+  <dimension ref="A1:B1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" style="3" customWidth="1"/>
@@ -790,37 +793,37 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -828,7 +831,7 @@
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -836,7 +839,7 @@
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -844,63 +847,63 @@
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="B8" s="2">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3">
         <v>42</v>
@@ -908,28 +911,35 @@
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B16" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1900,13 +1910,14 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="7">
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please provide a number between 0 and 2." promptTitle="Provide a number between 0 and 1" sqref="B5" xr:uid="{EFD0ACF5-0485-B148-809F-D3E4CDE614DF}">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please input an integer greater than 0." sqref="B15 B7:B8" xr:uid="{A7AC3B0A-A91E-3848-AFCF-9F6D356E061A}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please input an integer greater than 0." sqref="B7:B8 B15" xr:uid="{A7AC3B0A-A91E-3848-AFCF-9F6D356E061A}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose a treatment assignment strategy from the dropdown list." sqref="B9" xr:uid="{A0908BD7-278C-7644-ACEE-B0D30D664E7C}">
@@ -1918,7 +1929,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose a role assignment strategy from the dropdown list." sqref="B13" xr:uid="{CD5A8A2F-647C-7140-A110-46420E7F8C2F}">
       <formula1>"random, manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B16" xr:uid="{E2415674-B0C6-6543-8726-22265FD96C3A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B16:B17" xr:uid="{E2415674-B0C6-6543-8726-22265FD96C3A}">
       <formula1>"True, False"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please input an integer greater than 1." sqref="B6" xr:uid="{91A4D079-E77F-E543-AFF8-435F82B6DDF6}">
@@ -1935,33 +1946,34 @@
   <dimension ref="A1:B1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.1640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="3" customWidth="1"/>
     <col min="3" max="27" width="10.6640625" style="3" customWidth="1"/>
     <col min="28" max="16384" width="11.1640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>118</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>119</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2972,7 +2984,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B996"/>
+  <dimension ref="A1:B995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="3" customWidth="1"/>
@@ -2984,60 +2996,53 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>92</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
+      <c r="A6" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4026,7 +4031,6 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4035,7 +4039,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M852"/>
+  <dimension ref="A1:M849"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -4057,43 +4061,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4101,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -4110,16 +4114,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="3" t="b">
@@ -4140,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -4148,29 +4152,27 @@
       <c r="D3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>103</v>
+      <c r="E3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="3" t="b">
         <v>0</v>
@@ -4181,7 +4183,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -4190,19 +4192,19 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="J4" s="3" t="b">
         <v>1</v>
@@ -4222,7 +4224,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -4231,19 +4233,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="J5" s="3" t="b">
         <v>1</v>
@@ -4263,40 +4265,40 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
       </c>
       <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="J6" s="3" t="b">
-        <v>0</v>
       </c>
       <c r="K6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4304,28 +4306,28 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>106</v>
+        <v>71</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="J7" s="3" t="b">
         <v>0</v>
@@ -4334,135 +4336,15 @@
         <v>1</v>
       </c>
       <c r="L7" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="J8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="2">
-        <v>4</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="J10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5302,19 +5184,16 @@
     <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="D2:D1048576 J2:M1048576" xr:uid="{4BB7CE7C-18FC-BB40-9E15-025F5FDB5F2D}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="J2:M1048576 D2:D1048576" xr:uid="{4BB7CE7C-18FC-BB40-9E15-025F5FDB5F2D}">
       <formula1>"True, False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B2:B1048576" xr:uid="{04E1F09C-E3CF-9344-AD18-370A7D398746}">
-      <formula1>"context, public_question, private_question, discussion"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H2:H1048576" xr:uid="{C0EF5457-CD4D-5844-A648-AA1E0EA16788}">
       <formula1>"context, category, integer, free-text"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B2:B1048576" xr:uid="{9A8000B4-8EAB-FF46-8307-B16E6CDD6956}">
+      <formula1>"context, discussion, public_question, repeat_public_question, private_question, repeat_private_question"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -5336,144 +5215,144 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="E1" s="7" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="L2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="V2" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="M2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="W2" s="7" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5538,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="V3" s="3">
         <v>0</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5609,13 +5488,13 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="V4" s="3">
         <v>0</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5680,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="V5" s="3">
         <v>0</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5751,13 +5630,13 @@
         <v>0</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="V6" s="3">
         <v>0</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5822,13 +5701,13 @@
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="V7" s="3">
         <v>5</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5893,13 +5772,13 @@
         <v>1</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="V8" s="3">
         <v>5</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5964,13 +5843,13 @@
         <v>1</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="V9" s="3">
         <v>5</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6035,13 +5914,13 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="V10" s="3">
         <v>5</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21972,18 +21851,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/demos/public_good_experiment/public_good_experiment_prompt_template.xlsx
+++ b/demos/public_good_experiment/public_good_experiment_prompt_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raymondlow/Documents/talking-to-machines/talking-to-machines/demos/public_good_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231100AC-0422-4440-A56D-0B65BF63409F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC290FD-622C-5840-8251-BF4C1014E879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="2600" windowWidth="34560" windowHeight="19720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="880" windowWidth="22880" windowHeight="24220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>participant_label</t>
-  </si>
-  <si>
-    <t>["participant", "subject"]</t>
   </si>
   <si>
     <t>gender</t>
@@ -381,58 +378,6 @@
     <t>max_num_rounds</t>
   </si>
   <si>
-    <t>{
-"description":"Assume the role of a {{ constant.participant_label }} (Participant 1) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
-}</t>
-  </si>
-  <si>
-    <t>{
-"description":"Assume the role of a {{ constant.participant_label }} (Participant 2) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
-}</t>
-  </si>
-  <si>
-    <t>{
-"description":"Assume the role of a {{ constant.participant_label }} (Participant 3) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
-}</t>
-  </si>
-  <si>
-    <t>{
-"description":"Assume the role of a {{ constant.participant_label }} (Participant 4) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. 
-Example: 
-You have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you will see:
-- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
-- Your earnings from the public account.
-- Your private tokens kept from the round.
-- Your total earnings so far.
-Answer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response.",
-}</t>
-  </si>
-  <si>
     <t xml:space="preserve">General Overview
 Welcome to the public good experiment. You will be part of a group of 4 {{ constant.participant_label }}s, and you will interact with the same group throughout the experiment. The experiment consists of 5 rounds, and your decisions will affect both your earnings and the earnings of others in your group. All decisions are anonymous, and you will not know the identity of other {{ constant.participant_label }}s.
 1. Instructions
@@ -472,16 +417,6 @@
     <t>{"Participant 1": "Enter a number between 0 and 10", "Participant 2": "Enter a number between 0 and 10", "Participant 3": (0,10), "Participant 4": [0,1,2,3,4,5,6,7,8,9,10]}</t>
   </si>
   <si>
-    <t>{
-"Participant 1": "How many tokens do you want to contribute to the public account? {{ response_options }}",
-"Participant 2": "How many tokens do you want to contribute to the public account? {{ response_options }}",
-"Participant 3": "How many tokens do you want to contribute to the public account? {{ response_options }}",
-"Participant 4": "How many tokens do you want to contribute to the public account? {{ response_options }}",
-"facilitator": {{ role.calculate_payoff }},
-"facilitator": {{ role.end_round }},
-}</t>
-  </si>
-  <si>
     <t>Treatment 1</t>
   </si>
   <si>
@@ -489,20 +424,40 @@
   </si>
   <si>
     <t>{
-"description":"Assume the role of a facilitator in a public good experiment involving 4 {{ constant.participant_label }}s. Each {{ constant.participant_label }} will start with an initial endowment of 10 tokens. During each round of the experiment, each {{ constant.participant_label }} is asked to decide how many tokens to contribute to a public account and how many to keep in their private account. The tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in the {{ constant.participant_label }}s' private account will not be shared and remain private. 
-Example:
-A {{ constant.participant_label }} have 10 tokens. If that {{ constant.participant_label }} contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). The {{ constant.participant_label }} will keep the remaining 6 tokens in their private account. Contributions to the public account benefit everyone, including the {{ constant.participant_label }}. What they keep in their private account benefits only themselves. The total earnings for each round equal to private tokens kept + public tokens earned.
-At the end of each round, you are responsible for calculating the following information for each {{ constant.participant_label }}:
-- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
-- The {{ constant.participant_label }}'s earnings from the public account.
-- The {{ constant.participant_label }}'s private tokens kept from the round.
-- The {{ constant.participant_label }}'s total earnings so far.", 
-"calculate_payoff":"Calculate the following information for each {{ constant.participant_label }}:
-- The total tokens contributed to the public account by all {{ constant.participant_label }}s.
-- The {{ constant.participant_label }}'s earnings from the public account.
-- The {{ constant.participant_label }}'s private tokens kept from the round.
-- The {{ constant.participant_label }}'s total earnings so far.",
-"end_round":"Evaluate the number of times that the group has repeated this round and return the following command if the group has completed this round at least five times: 'end_round' "
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 1) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. \n\nExample: \nYou have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.\n\nAt the end of each round, you will see:\n- The total tokens contributed to the public account by all {{ constant.participant_label }}s.\n- Your earnings from the public account.\n- Your private tokens kept from the round.\n- Your total earnings so far.\n\nAnswer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 2) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. \n\nExample: \nYou have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.\n\nAt the end of each round, you will see:\n- The total tokens contributed to the public account by all {{ constant.participant_label }}s.\n- Your earnings from the public account.\n- Your private tokens kept from the round.\n- Your total earnings so far.\n\nAnswer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 3) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. \n\nExample: \nYou have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.\n\nAt the end of each round, you will see:\n- The total tokens contributed to the public account by all {{ constant.participant_label }}s.\n- Your earnings from the public account.\n- Your private tokens kept from the round.\n- Your total earnings so far.\n\nAnswer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a {{ constant.participant_label }} (Participant 4) in a public good experiment involving 3 other {{ constant.participant_label }}s. You will start with an initial endowment of 10 tokens. During each round of the experiment, you must decide how many tokens to contribute to a public account and how many to keep in your private account. Tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in your private account will not be shared and remain yours. \n\nExample: \nYou have 10 tokens. If you contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). You will keep the remaining 6 tokens in your private account. Contributions to the public account benefit everyone, including you. What you keep in your private account benefits only you. Your total earnings for each round equal to private tokens kept + public tokens earned.\n\nAt the end of each round, you will see:\n- The total tokens contributed to the public account by all {{ constant.participant_label }}s.\n- Your earnings from the public account.\n- Your private tokens kept from the round.\n- Your total earnings so far.\n\nAnswer any question that is posed to you in as much detail as possible and in the format required. Please provide a consistent and coherent response using all the demographic information provided about you. It is crucial for you to accurately replicate the response of a human subject that has the demographic profile you are provided. The human subject response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Do not include your name in your response."
+}</t>
+  </si>
+  <si>
+    <t>["participant"]</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a facilitator in a public good experiment involving 4 {{ constant.participant_label }}s. Each {{ constant.participant_label }} will start with an initial endowment of 10 tokens. During each round of the experiment, each {{ constant.participant_label }} is asked to decide how many tokens to contribute to a public account and how many to keep in their private account. The tokens contributed to the public account will be multipled by a factor of 2 and distributed equally among all group members after each round. Tokens kept in the {{ constant.participant_label }}s' private account will not be shared and remain private. \n\nExample:\nA {{ constant.participant_label }} have 10 tokens. If that {{ constant.participant_label }} contribute 4 tokens to the public account: These 4 tokens are doubled to 8 and shared equally among the group. Each group member receives 2 tokens (8 / 4). The {{ constant.participant_label }} will keep the remaining 6 tokens in their private account. Contributions to the public account benefit everyone, including the {{ constant.participant_label }}. What they keep in their private account benefits only themselves. The total earnings for each round equal to private tokens kept + public tokens earned.\n\nAt the end of each round, you are responsible for calculating the following information for each {{ constant.participant_label }}:\n- The total tokens contributed to the public account by all {{ constant.participant_label }}s.\n- The {{ constant.participant_label }}'s earnings from the public account.\n- The {{ constant.participant_label }}'s private tokens kept from the round.\n- The {{ constant.participant_label }}'s total earnings so far.", 
+"calculate_payoff":"Calculate the following information for each {{ constant.participant_label }}:\n- The total tokens contributed to the public account by all {{ constant.participant_label }}s.\n- The {{ constant.participant_label }}'s earnings from the public account.\n- The {{ constant.participant_label }}'s private tokens kept from the round.\n- The {{ constant.participant_label }}'s total earnings so far. \nAfter performing these calculation for each {{ constant.participant_label }}, evaluate the number of times the group has repeated this round. Return the command 'end_round' if the group has completed this round at least five times; otherwise, return the command 'continue_round'."
+}</t>
+  </si>
+  <si>
+    <t>{
+"Participant 1": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"Participant 2": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"Participant 3": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"Participant 4": "How many tokens do you want to contribute to the public account? {{ response_options }}",
+"facilitator": "{{ role.calculate_payoff }}",
 }</t>
   </si>
 </sst>
@@ -510,7 +465,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -528,6 +483,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -547,10 +509,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -568,8 +531,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -793,7 +758,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -801,10 +766,10 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -812,14 +777,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="B4" s="9"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -831,7 +796,7 @@
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -839,7 +804,7 @@
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -847,10 +812,10 @@
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -871,7 +836,7 @@
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
@@ -879,10 +844,10 @@
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -898,7 +863,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -911,18 +876,18 @@
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1946,7 +1911,7 @@
   <dimension ref="A1:B1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.1640625" style="3" customWidth="1"/>
     <col min="3" max="27" width="10.6640625" style="3" customWidth="1"/>
     <col min="28" max="16384" width="11.1640625" style="3"/>
@@ -1962,18 +1927,18 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3004,42 +2969,42 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4061,13 +4026,13 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>10</v>
@@ -4079,10 +4044,10 @@
         <v>12</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>13</v>
@@ -4114,10 +4079,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>18</v>
@@ -4153,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>7</v>
@@ -4192,19 +4157,19 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J4" s="3" t="b">
         <v>1</v>
@@ -4233,19 +4198,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J5" s="3" t="b">
         <v>1</v>
@@ -4274,19 +4239,19 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J6" s="3" t="b">
         <v>1</v>
@@ -4306,7 +4271,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
@@ -4315,19 +4280,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J7" s="3" t="b">
         <v>0</v>
@@ -5218,70 +5183,70 @@
         <v>20</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="U1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
@@ -5289,70 +5254,70 @@
         <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="U2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="V2" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5417,13 +5382,13 @@
         <v>0</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="V3" s="3">
         <v>0</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5488,13 +5453,13 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="V4" s="3">
         <v>0</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5559,13 +5524,13 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="V5" s="3">
         <v>0</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5630,13 +5595,13 @@
         <v>0</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="V6" s="3">
         <v>0</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5701,13 +5666,13 @@
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="V7" s="3">
         <v>5</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5772,13 +5737,13 @@
         <v>1</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="V8" s="3">
         <v>5</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5843,13 +5808,13 @@
         <v>1</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="V9" s="3">
         <v>5</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5914,13 +5879,13 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="V10" s="3">
         <v>5</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21851,7 +21816,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -21862,7 +21827,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/demos/public_good_experiment/public_good_experiment_prompt_template.xlsx
+++ b/demos/public_good_experiment/public_good_experiment_prompt_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raymondlow/Documents/talking-to-machines/talking-to-machines/demos/public_good_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC290FD-622C-5840-8251-BF4C1014E879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C626BF3F-E561-584E-B118-36DBD194514C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="880" windowWidth="22880" windowHeight="24220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-760" yWindow="-21100" windowWidth="26660" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -815,7 +815,7 @@
         <v>105</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -887,7 +887,7 @@
         <v>86</v>
       </c>
       <c r="B17" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
